--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486392_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486392_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2977</v>
+        <v>4.1292</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9557</v>
+        <v>3.6947</v>
       </c>
       <c r="F2" t="n">
-        <v>0.342</v>
+        <v>0.4345</v>
       </c>
       <c r="G2" t="n">
         <v>1.7086</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1064</v>
+        <v>-0.2749</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8784</v>
+        <v>-0.1394</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.228</v>
+        <v>-0.1355</v>
       </c>
       <c r="V2" t="n">
         <v>0.9554</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6855</v>
+        <v>3.8339</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3647</v>
+        <v>3.4823</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3208</v>
+        <v>0.3516</v>
       </c>
       <c r="G3" t="n">
         <v>2.6776</v>
@@ -688,13 +688,13 @@
         <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.382</v>
+        <v>0.7664</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.399</v>
+        <v>0.7186</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0169</v>
+        <v>0.0478</v>
       </c>
       <c r="V3" t="n">
         <v>1.695</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4419</v>
+        <v>2.9805</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7307</v>
+        <v>2.0227</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.9578</v>
       </c>
       <c r="G4" t="n">
         <v>0.6955</v>
@@ -766,13 +766,13 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3836</v>
+        <v>0.155</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2139</v>
+        <v>0.0781</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1697</v>
+        <v>0.0769</v>
       </c>
       <c r="V4" t="n">
         <v>1.695</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. VAN ZEGEREN</t>
+          <t>O. LO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2651</v>
+        <v>0.6206</v>
       </c>
       <c r="E5" t="n">
-        <v>2.168</v>
+        <v>0.2895</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9029</v>
+        <v>0.3311</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2763</v>
+        <v>-0.9847</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1632</v>
+        <v>-0.9791</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1131</v>
+        <v>-0.0056</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9004</v>
+        <v>1.0834</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7474</v>
+        <v>0.8156</v>
       </c>
       <c r="L5" t="n">
-        <v>0.153</v>
+        <v>0.2677</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6241</v>
+        <v>-2.0681</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5843</v>
+        <v>-1.7948</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0399</v>
+        <v>-0.2733</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9576</v>
+        <v>2.3926</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9029</v>
+        <v>0.453</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4443</v>
+        <v>0.2512</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5414</v>
+        <v>0.2019</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.609</v>
+        <v>0.9347</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.9141</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.695</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. LO</t>
+          <t>J. PAUKSTÈ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0907</v>
+        <v>0.5421</v>
       </c>
       <c r="E6" t="n">
-        <v>0.513</v>
+        <v>0.9507</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5777</v>
+        <v>-0.4086</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9847</v>
+        <v>0.0133</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9791</v>
+        <v>0.0213</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0056</v>
+        <v>-0.008</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0834</v>
+        <v>0.6787</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8156</v>
+        <v>0.6022</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2677</v>
+        <v>0.0765</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0681</v>
+        <v>-0.6654</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.7948</v>
+        <v>-0.581</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2733</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P6" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-1.0875</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.2175</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-2.1751</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.3926</v>
-      </c>
       <c r="S6" t="n">
-        <v>0.9231</v>
+        <v>0.2689</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4747</v>
+        <v>0.2295</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4485</v>
+        <v>0.0394</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9347</v>
+        <v>1.13</v>
       </c>
       <c r="W6" t="n">
         <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PAUKSTÈ</t>
+          <t>C. ROGERS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0816</v>
+        <v>0.3848</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3977</v>
+        <v>0.3836</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3161</v>
+        <v>0.0012</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0133</v>
+        <v>0.8429</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0213</v>
+        <v>-1.77</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.008</v>
+        <v>2.6129</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6787</v>
+        <v>2.3436</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6022</v>
+        <v>-0.3737</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0765</v>
+        <v>2.7173</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6654</v>
+        <v>-1.5007</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.581</v>
+        <v>-1.3963</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.1044</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.87</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2175</v>
+        <v>2.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8084</v>
+        <v>-0.2629</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6766</v>
+        <v>0.2151</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1318</v>
+        <v>-0.478</v>
       </c>
       <c r="V7" t="n">
-        <v>1.13</v>
+        <v>-0.1952</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MARTINEZ CLARIANA</t>
+          <t>J. VAN ZEGEREN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7036</v>
+        <v>0.3017</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0449</v>
+        <v>1.0505</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6587</v>
+        <v>-0.7488</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.6857</v>
+        <v>3.2763</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6083</v>
+        <v>3.1632</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0774</v>
+        <v>0.1131</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.495</v>
+        <v>3.9004</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.903</v>
+        <v>3.7474</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5921</v>
+        <v>0.153</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1907</v>
+        <v>-0.6241</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2947</v>
+        <v>-0.5843</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4854</v>
+        <v>-0.0399</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5225</v>
+        <v>-1.305</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6716</v>
+        <v>0.9394</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3447</v>
+        <v>1.3267</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3268</v>
+        <v>-0.3873</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1952</v>
+        <v>-2.609</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1952</v>
+        <v>-0.9141</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. ROGERS</t>
+          <t>A. MARTINEZ CLARIANA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0688</v>
+        <v>0.0169</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1601</v>
+        <v>-0.3336</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.3505</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8429</v>
+        <v>-2.6857</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.77</v>
+        <v>-0.6083</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6129</v>
+        <v>-2.0774</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3436</v>
+        <v>-1.495</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3737</v>
+        <v>-0.903</v>
       </c>
       <c r="L9" t="n">
-        <v>2.7173</v>
+        <v>-0.5921</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5007</v>
+        <v>-1.1907</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3963</v>
+        <v>0.2947</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1044</v>
+        <v>-1.4854</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>1.5225</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1751</v>
+        <v>1.5225</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5789</v>
+        <v>0.9848</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5705</v>
+        <v>0.0186</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1952</v>
+        <v>0.1952</v>
       </c>
       <c r="W9" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="X9" t="n">
         <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-0.1952</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1075</v>
+        <v>-0.0776</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.379</v>
+        <v>-2.534</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2714</v>
+        <v>2.4564</v>
       </c>
       <c r="G10" t="n">
         <v>-2.8067</v>
@@ -1234,13 +1234,13 @@
         <v>2.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.7493</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7487</v>
+        <v>0.5936</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0293</v>
+        <v>0.1556</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1952</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4628</v>
+        <v>-0.6294</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0573</v>
+        <v>-1.1005</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5944</v>
+        <v>0.4712</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9647</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5018</v>
+        <v>0.3353</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0601</v>
+        <v>0.0168</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4417</v>
+        <v>0.3184</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.439</v>
+        <v>-2.1345</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7897</v>
+        <v>-2.4545</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3508</v>
+        <v>0.3199</v>
       </c>
       <c r="G12" t="n">
         <v>0.2276</v>
@@ -1390,13 +1390,13 @@
         <v>1.7401</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7536</v>
+        <v>-0.4491</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8904</v>
+        <v>-0.5552</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1369</v>
+        <v>0.106</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3904</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.625600000000002</v>
+        <v>9.9682</v>
       </c>
       <c r="E13" t="n">
-        <v>5.108800000000002</v>
+        <v>5.4514</v>
       </c>
       <c r="F13" t="n">
-        <v>4.5167</v>
+        <v>4.516799999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1.999999999999999</v>
       </c>
       <c r="H13" t="n">
         <v>-1.8248</v>
@@ -1468,16 +1468,16 @@
         <v>18.4882</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3226</v>
+        <v>3.6652</v>
       </c>
       <c r="T13" t="n">
-        <v>3.359</v>
+        <v>3.7012</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.03629999999999992</v>
+        <v>-0.03619999999999989</v>
       </c>
       <c r="V13" t="n">
-        <v>3.2155</v>
+        <v>3.215500000000001</v>
       </c>
       <c r="W13" t="n">
         <v>7.0164</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2039</v>
+        <v>2.4261</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9213</v>
+        <v>0.8095</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2826</v>
+        <v>1.6166</v>
       </c>
       <c r="G14" t="n">
         <v>1.2208</v>
@@ -1546,13 +1546,13 @@
         <v>2.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2997</v>
+        <v>-0.0775</v>
       </c>
       <c r="T14" t="n">
-        <v>0.08409999999999999</v>
+        <v>-0.0276</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3838</v>
+        <v>-0.0499</v>
       </c>
       <c r="V14" t="n">
         <v>0.1952</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. CRUZ UCEDA</t>
+          <t>P. KRUTOUS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3997</v>
+        <v>1.3419</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0125</v>
+        <v>0.8612</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6128</v>
+        <v>0.4807</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4439</v>
+        <v>-0.0143</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0063</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4375</v>
+        <v>-0.8718</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8499</v>
+        <v>0.7278</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0561</v>
+        <v>0.8791</v>
       </c>
       <c r="L15" t="n">
-        <v>2.7938</v>
+        <v>-0.1514</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.406</v>
+        <v>-0.7421</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0497</v>
+        <v>-0.0217</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3563</v>
+        <v>-0.7204</v>
       </c>
       <c r="P15" t="n">
-        <v>0.435</v>
+        <v>1.9576</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.6101</v>
+        <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2157</v>
+        <v>-0.0363</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3377</v>
+        <v>0.1334</v>
       </c>
       <c r="U15" t="n">
-        <v>0.878</v>
+        <v>-0.1698</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.695</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.695</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. KRUTOUS</t>
+          <t>I. CRUZ UCEDA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3767</v>
+        <v>0.308</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4199</v>
+        <v>1.789</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0433</v>
+        <v>-1.481</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0143</v>
+        <v>1.4439</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.0063</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8718</v>
+        <v>1.4375</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7278</v>
+        <v>3.8499</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8791</v>
+        <v>1.0561</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1514</v>
+        <v>2.7938</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7421</v>
+        <v>-2.406</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0217</v>
+        <v>-1.0497</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7204</v>
+        <v>-1.3563</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9576</v>
+        <v>0.435</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9576</v>
+        <v>2.6101</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0016</v>
+        <v>0.1241</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6922</v>
+        <v>0.1142</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6937</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.695</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5371</v>
+        <v>-0.2233</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0782</v>
+        <v>-1.5252</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6153</v>
+        <v>1.302</v>
       </c>
       <c r="G17" t="n">
         <v>-1.3246</v>
@@ -1780,13 +1780,13 @@
         <v>2.6101</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5137</v>
+        <v>-0.2466</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4867</v>
+        <v>0.0397</v>
       </c>
       <c r="U17" t="n">
-        <v>0.027</v>
+        <v>-0.2863</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1745</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5333</v>
+        <v>-0.2532</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.056</v>
+        <v>-0.8324</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.5792</v>
       </c>
       <c r="G18" t="n">
         <v>3.3426</v>
@@ -1858,13 +1858,13 @@
         <v>2.3926</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2568</v>
+        <v>0.5369</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2211</v>
+        <v>0.4446</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0357</v>
+        <v>0.0922</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. PALOMARES CALDERON</t>
+          <t>C. DIAZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9182</v>
+        <v>-1.6809</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3402</v>
+        <v>0.5291</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2584</v>
+        <v>-2.2101</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5708</v>
+        <v>-2.4958</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9915</v>
+        <v>-1.624</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4207</v>
+        <v>-0.8718</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4772</v>
+        <v>0.5708</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7086</v>
+        <v>0.3197</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1857</v>
+        <v>0.251</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0479</v>
+        <v>-3.0666</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2829</v>
+        <v>-1.9438</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.765</v>
+        <v>-1.1228</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2175</v>
+        <v>1.9576</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2175</v>
+        <v>3.0451</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.435</v>
+        <v>-0.7523</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.137</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.298</v>
+        <v>-0.6682</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. DIAZ RODRIGUEZ</t>
+          <t>C. PALOMARES CALDERON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7098</v>
+        <v>-1.8065</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2532</v>
+        <v>0.4519</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4567</v>
+        <v>-2.2584</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4958</v>
+        <v>-0.5708</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.624</v>
+        <v>-0.9915</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8718</v>
+        <v>0.4207</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5708</v>
+        <v>0.4772</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3197</v>
+        <v>-0.7086</v>
       </c>
       <c r="L20" t="n">
-        <v>0.251</v>
+        <v>1.1857</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.0666</v>
+        <v>-1.0479</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.9438</v>
+        <v>-0.2829</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1228</v>
+        <v>-0.765</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9576</v>
+        <v>0.2175</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.0451</v>
+        <v>0.2175</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7812</v>
+        <v>-0.3233</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8663999999999999</v>
+        <v>-0.0252</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9147</v>
+        <v>-0.298</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3904</v>
+        <v>-1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.5204</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6024</v>
+        <v>-3.3982</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8135</v>
+        <v>-0.7017</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7889</v>
+        <v>-2.6965</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0388</v>
@@ -2092,13 +2092,13 @@
         <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1509</v>
+        <v>-0.9466</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4675</v>
+        <v>-0.3557</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6834</v>
+        <v>-0.5909</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7602</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.3792</v>
+        <v>-5.5944</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.0098</v>
+        <v>-5.898</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3694</v>
+        <v>0.3036</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5629</v>
@@ -2170,13 +2170,13 @@
         <v>1.9576</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6407</v>
+        <v>-0.8559</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3148</v>
+        <v>-0.2031</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.3258</v>
+        <v>-0.6528</v>
       </c>
       <c r="V22" t="n">
         <v>1.3045</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.625499999999999</v>
+        <v>-8.880500000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5168</v>
+        <v>-4.5166</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.108899999999999</v>
+        <v>-4.3639</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9999</v>
@@ -2239,7 +2239,7 @@
         <v>-5.7137</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.0875</v>
+        <v>-1.087500000000001</v>
       </c>
       <c r="Q23" t="n">
         <v>-18.488</v>
@@ -2248,13 +2248,13 @@
         <v>17.4007</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.3229</v>
+        <v>-2.5775</v>
       </c>
       <c r="T23" t="n">
-        <v>0.03610000000000019</v>
+        <v>0.03619999999999995</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.3587</v>
+        <v>-2.6138</v>
       </c>
       <c r="V23" t="n">
         <v>-3.2154</v>
@@ -2263,7 +2263,7 @@
         <v>3.8011</v>
       </c>
       <c r="X23" t="n">
-        <v>-7.016499999999999</v>
+        <v>-7.0165</v>
       </c>
     </row>
   </sheetData>
